--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל בנשלום – ממשיך ליפול</v>
+        <v>מייפל Wishing for peace</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%91%d7%a0%d7%a9%d7%9c%d7%95%d7%9d-%d7%9e%d7%9e%d7%a9%d7%99%d7%9a-%d7%9c%d7%99%d7%a4%d7%95%d7%9c/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%a4%d7%9c-wishing-for-peace/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יובל בנשלום שר שיר עדין קשה, שכוחו נובע דווקא מהעובדה שהוא לא מנסה לפתור את הדיכאון – אלא להיות לידו. זהו שיר על אהבה תחת דיכאון, נאמנות של אוהבת שלא יודעת איך לעזור, פער כואב בין רצון למציאות הבחירה לספר</v>
+        <v>מייפל שרה שיר בעל משקל היסטורי ורגשי עצום. “Wishing for Peace” הוא שיר פולק, שנולד מעדות משפחתית. הבחירה בבלדת פולק מיד־טמפו איננה מקרית. פולק הוא ז’אנר של סיפורים, מסורת והעברה בין דורות. הקצב האמצעי מתניע דרמה. של הליכה מתמשכת זו</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל בנשלום – ממשיך ליפול</v>
+        <v>מייפל Wishing for peace</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מייפל Wishing for peace</v>
+        <v>אליעד ולירון עמרם – עוד שבוע</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%a4%d7%9c-wishing-for-peace/</v>
+        <v>https://yosmusic.com/%d7%90%d7%9c%d7%99%d7%a2%d7%93-%d7%95%d7%9c%d7%99%d7%a8%d7%95%d7%9f-%d7%a2%d7%9e%d7%a8%d7%9d-%d7%a2%d7%95%d7%93-%d7%a9%d7%91%d7%95%d7%a2/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-09</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מייפל שרה שיר בעל משקל היסטורי ורגשי עצום. “Wishing for Peace” הוא שיר פולק, שנולד מעדות משפחתית. הבחירה בבלדת פולק מיד־טמפו איננה מקרית. פולק הוא ז’אנר של סיפורים, מסורת והעברה בין דורות. הקצב האמצעי מתניע דרמה. של הליכה מתמשכת זו</v>
+        <v>הלב של השיר הוא רעיון אחד, שחוזר שוב ושוב: הזמן לא זז בלעדיה. ראשון שני שלישי והימים כבר לא עוברים אצלו. זהו תיאור  קלישאתי שאומר אכזריות הזמן – ספירת ימים, תלישת דפים, שעון, שבתות וחגים. הכול מוכר, הכול עובד, אבל</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מייפל Wishing for peace</v>
+        <v>אליעד ולירון עמרם – עוד שבוע</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אליעד ולירון עמרם – עוד שבוע</v>
+        <v>מיסטר הבי ומיס לואו – Not everything you wanted</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%9c%d7%99%d7%a2%d7%93-%d7%95%d7%9c%d7%99%d7%a8%d7%95%d7%9f-%d7%a2%d7%9e%d7%a8%d7%9d-%d7%a2%d7%95%d7%93-%d7%a9%d7%91%d7%95%d7%a2/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a1%d7%98%d7%a8-%d7%94%d7%91%d7%99-%d7%95%d7%9e%d7%99%d7%a1-%d7%9c%d7%95%d7%90%d7%95-not-everything-you-wanted/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-09</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הלב של השיר הוא רעיון אחד, שחוזר שוב ושוב: הזמן לא זז בלעדיה. ראשון שני שלישי והימים כבר לא עוברים אצלו. זהו תיאור  קלישאתי שאומר אכזריות הזמן – ספירת ימים, תלישת דפים, שעון, שבתות וחגים. הכול מוכר, הכול עובד, אבל</v>
+        <v>. “Not Everything You Wanted” של מיסטר הבי אנד מיס לואו (Mr. Heavy &amp; Ms. Low) הוא שיר מעבר  לא רק גיאוגרפי (עיר-כפר), אלא קיומי. שיר על בחירה שמכילה ויתור, אימהות בלי אידיאליזציה, חיים כפריים כמרחב של גילוי, לא של</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אליעד ולירון עמרם – עוד שבוע</v>
+        <v>מיסטר הבי ומיס לואו – Not everything you wanted</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיסטר הבי ומיס לואו – Not everything you wanted</v>
+        <v>שלומי שבן אלון עדר – עברנו לצפון קרית שמונה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a1%d7%98%d7%a8-%d7%94%d7%91%d7%99-%d7%95%d7%9e%d7%99%d7%a1-%d7%9c%d7%95%d7%90%d7%95-not-everything-you-wanted/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%9f-%d7%90%d7%9c%d7%95%d7%9f-%d7%a2%d7%93%d7%a8-%d7%a2%d7%91%d7%a8%d7%a0%d7%95-%d7%9c%d7%a6%d7%a4%d7%95%d7%9f-%d7%a7%d7%a8%d7%99%d7%aa-%d7%a9%d7%9e%d7%95/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>. “Not Everything You Wanted” של מיסטר הבי אנד מיס לואו (Mr. Heavy &amp; Ms. Low) הוא שיר מעבר  לא רק גיאוגרפי (עיר-כפר), אלא קיומי. שיר על בחירה שמכילה ויתור, אימהות בלי אידיאליזציה, חיים כפריים כמרחב של גילוי, לא של</v>
+        <v>אני מנסה לקרוא/ לחוש מאת המשאפ הזה בין שלומי שבן ואלון עדר לא רק כחיבור טכני בין שני שירים – אלא כטקסט אחד שמספר סיפור עם התפתחות רגשית ומוזיקלית. החיבור בין "עברנו לצפון” (שלומי שבן) ל־"קריית שמונה” (אלון עדר) מנסה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיסטר הבי ומיס לואו – Not everything you wanted</v>
+        <v>שלומי שבן אלון עדר – עברנו לצפון קרית שמונה</v>
       </c>
     </row>
   </sheetData>
